--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -705,11 +705,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>平62・3</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
@@ -1187,7 +1183,7 @@
       <c r="L27" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="60">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="G2:H2"/>
@@ -1205,6 +1201,7 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="J23:K23"/>
     <mergeCell ref="A14:F14"/>
@@ -1246,8 +1243,6 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="H5:L5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,17 @@
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -189,59 +194,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,7 +255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,24 +625,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.66666666666667" customWidth="1" min="1" max="1"/>
-    <col width="12.66666666666667" customWidth="1" min="2" max="2"/>
-    <col width="12.66666666666667" customWidth="1" min="3" max="3"/>
-    <col width="12.66666666666667" customWidth="1" min="4" max="4"/>
-    <col width="12.66666666666667" customWidth="1" min="5" max="5"/>
-    <col width="12.66666666666667" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="45" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>製造指図書</t>
@@ -658,7 +660,7 @@
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>手配No.</t>
@@ -671,29 +673,33 @@
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2018/12/05</t>
         </is>
       </c>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>手配先</t>
         </is>
@@ -706,24 +712,24 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>手配納期</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2018/12/14</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>品目CD</t>
         </is>
@@ -735,32 +741,32 @@
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>工順</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>発注手配数</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>400.72 kg</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>品目名</t>
@@ -769,28 +775,28 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
+          <t>クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>製番</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>0000051090</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>手配内容</t>
@@ -805,22 +811,22 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>完成入庫</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>S00000200 製造1課 倉庫</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ロットNo.</t>
@@ -831,18 +837,18 @@
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>完成日</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>調合票</t>
@@ -861,89 +867,89 @@
       <c r="L8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>成分名</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>原単位</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>秤量者</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>原料ロット</t>
         </is>
       </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>HA0002610　　100 仕込
-クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>HA0002610  100 仕込
+クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>100.0000</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>400.72
 kg</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr"/>
-      <c r="J11" s="13" t="inlineStr"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="15" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>H00001630　　999 購入
+      <c r="J11" s="12" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>H00001630  999 購入
 クラフト袋L イージーオープン</t>
         </is>
       </c>
@@ -952,298 +958,289 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>8.3334</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>33.40
 枚</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="19" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="16" t="inlineStr"/>
+      <c r="L12" s="18" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="20" t="n"/>
+      <c r="A13" s="19" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="21" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="20" t="n"/>
+      <c r="A14" s="19" t="n"/>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="22" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="20" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="21" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="20" t="n"/>
+      <c r="A15" s="19" t="n"/>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="22" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="21" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="20" t="n"/>
+      <c r="A16" s="19" t="n"/>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="22" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="21" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="20" t="n"/>
+      <c r="A17" s="19" t="n"/>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="22" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="20" t="n"/>
+      <c r="K17" s="20" t="n"/>
+      <c r="L17" s="21" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="20" t="n"/>
+      <c r="A18" s="19" t="n"/>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="22" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="21" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="20" t="n"/>
+      <c r="A19" s="19" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="22" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="20" t="n"/>
+      <c r="J19" s="20" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="21" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="20" t="n"/>
+      <c r="A20" s="19" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="22" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="21" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="20" t="n"/>
+      <c r="A21" s="19" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="22" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="21" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="20" t="n"/>
+      <c r="A22" s="19" t="n"/>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="22" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="L22" s="21" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="20" t="n"/>
+      <c r="A23" s="19" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="22" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="20" t="n"/>
+      <c r="J23" s="20" t="n"/>
+      <c r="K23" s="20" t="n"/>
+      <c r="L23" s="21" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="20" t="n"/>
+      <c r="A24" s="19" t="n"/>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="22" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
+      <c r="L24" s="21" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="20" t="n"/>
+      <c r="A25" s="19" t="n"/>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="22" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="20" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="20" t="n"/>
+      <c r="J25" s="20" t="n"/>
+      <c r="K25" s="20" t="n"/>
+      <c r="L25" s="21" t="n"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="24" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
-      <c r="G27" s="24" t="n"/>
-      <c r="H27" s="24" t="n"/>
-      <c r="I27" s="24" t="n"/>
-      <c r="J27" s="24" t="n"/>
-      <c r="K27" s="24" t="n"/>
-      <c r="L27" s="25" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="23" t="n"/>
+      <c r="L26" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="65">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="A9:F10"/>
-    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H2:J2"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="H4:L4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="G23:H23"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="J23:K23"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J15:K15"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="G13:H13"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="J3:L3"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="C2:D2"/>
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="J16:K16"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G14:H14"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="J9:K10"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,21 +33,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <sz val="22"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -68,99 +58,139 @@
     </border>
     <border>
       <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
-      <top style="thin"/>
+      <top/>
       <bottom style="thin"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
     </border>
     <border>
       <left style="medium"/>
-      <right style="thin"/>
+      <right/>
       <top style="medium"/>
-      <bottom style="thin"/>
+      <bottom/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="medium"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top style="medium"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="thin"/>
+      <right/>
       <top style="medium"/>
       <bottom style="thin"/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
       <left style="medium"/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
       <left style="medium"/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
@@ -169,23 +199,9 @@
       <right/>
       <top style="thin"/>
       <bottom style="medium"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="thin"/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="medium"/>
@@ -194,72 +210,104 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -625,21 +673,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="5.7265625" customWidth="1" min="1" max="1"/>
+    <col width="8.43" customWidth="1" min="2" max="2"/>
+    <col width="8.43" customWidth="1" min="3" max="3"/>
+    <col width="8.43" customWidth="1" min="4" max="4"/>
+    <col width="8.43" customWidth="1" min="5" max="5"/>
+    <col width="8.43" customWidth="1" min="6" max="6"/>
+    <col width="8.43" customWidth="1" min="7" max="7"/>
+    <col width="8.43" customWidth="1" min="8" max="8"/>
+    <col width="8.43" customWidth="1" min="9" max="9"/>
+    <col width="8.43" customWidth="1" min="10" max="10"/>
+    <col width="8.43" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8.43" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="8.43" customWidth="1" min="15" max="15"/>
+    <col width="8.43" customWidth="1" min="16" max="16"/>
+    <col width="8.43" customWidth="1" min="17" max="17"/>
+    <col width="6.6328125" customWidth="1" min="18" max="18"/>
+    <col width="8.43" customWidth="1" min="19" max="19"/>
+    <col width="8.43" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="8.43" customWidth="1" min="22" max="22"/>
+    <col width="8.43" customWidth="1" min="23" max="23"/>
+    <col width="8.43" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -659,588 +719,1137 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="3" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>手配No.</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>0000056473</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2018/12/05</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>作成者</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>2018/12/14</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="5" t="n"/>
+      <c r="V2" s="5" t="n"/>
+      <c r="W2" s="5" t="n"/>
+      <c r="X2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+      <c r="O3" s="7" t="n"/>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+      <c r="R3" s="7" t="n"/>
+      <c r="S3" s="7" t="n"/>
+      <c r="T3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
+      <c r="W3" s="7" t="n"/>
+      <c r="X3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>手配先</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>S00000200 製造1課 倉庫</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>手配納期</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>2018/12/14</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>S000002 製造１課　倉庫</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="9" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>手配調整期</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>S000002 製造１課　倉庫</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="9" t="n"/>
+      <c r="U4" s="9" t="n"/>
+      <c r="V4" s="9" t="n"/>
+      <c r="W4" s="9" t="n"/>
+      <c r="X4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>品目CD</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>HA0002610</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>工順</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>発注手配数</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>400.72 kg</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="P5" s="12" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="12" t="n"/>
+      <c r="T5" s="12" t="n"/>
+      <c r="U5" s="12" t="n"/>
+      <c r="V5" s="12" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="13" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>品目名</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>ネイジーマキアップ サテン(37才混血)連絡品</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>製番</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="13" t="n"/>
+      <c r="R6" s="12" t="inlineStr">
         <is>
           <t>0000051090</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="n"/>
+      <c r="V6" s="12" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>手配内容</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>30　噴霧</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>完成入庫</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>S00000200 製造1課 倉庫</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="P7" s="12" t="n"/>
+      <c r="Q7" s="13" t="n"/>
+      <c r="R7" s="12" t="inlineStr">
+        <is>
+          <t>S000002 製造１課　倉庫</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="12" t="n"/>
+      <c r="U7" s="12" t="n"/>
+      <c r="V7" s="12" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>ロットNo.</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>完成日</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="13" t="n"/>
+      <c r="R8" s="12" t="n"/>
+      <c r="S8" s="12" t="n"/>
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="12" t="n"/>
+      <c r="V8" s="12" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="13" t="n"/>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>調合票</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
+      <c r="P9" s="14" t="n"/>
+      <c r="Q9" s="14" t="n"/>
+      <c r="R9" s="14" t="n"/>
+      <c r="S9" s="14" t="n"/>
+      <c r="T9" s="14" t="n"/>
+      <c r="U9" s="14" t="n"/>
+      <c r="V9" s="14" t="n"/>
+      <c r="W9" s="14" t="n"/>
+      <c r="X9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="14.5" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>成分名</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="17" t="n"/>
+      <c r="L10" s="18" t="inlineStr">
         <is>
           <t>原単位</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="18" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>秤量者</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="O10" s="17" t="n"/>
+      <c r="P10" s="18" t="inlineStr">
+        <is>
+          <t>検量者</t>
+        </is>
+      </c>
+      <c r="Q10" s="17" t="n"/>
+      <c r="R10" s="18" t="inlineStr">
         <is>
           <t>原料ロット</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>HA0002610  100 仕込
-クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="S10" s="16" t="n"/>
+      <c r="T10" s="16" t="n"/>
+      <c r="U10" s="16" t="n"/>
+      <c r="V10" s="17" t="n"/>
+      <c r="W10" s="16" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="X10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="20" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="24" t="n"/>
+      <c r="S11" s="20" t="n"/>
+      <c r="T11" s="20" t="n"/>
+      <c r="U11" s="20" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="20" t="n"/>
+      <c r="X11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>HA0002610        100 仕込
+ネイジーマキアップ サテン(37才混血)連絡品</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="27" t="n"/>
+      <c r="L12" s="28" t="inlineStr">
         <is>
           <t>100.0000</t>
         </is>
       </c>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="M12" s="27" t="n"/>
+      <c r="N12" s="28" t="inlineStr">
         <is>
           <t>400.72
 kg</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr"/>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>H00001630  999 購入
-クラフト袋L イージーオープン</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="O12" s="27" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="27" t="n"/>
+      <c r="R12" s="28" t="n"/>
+      <c r="S12" s="26" t="n"/>
+      <c r="T12" s="26" t="n"/>
+      <c r="U12" s="26" t="n"/>
+      <c r="V12" s="27" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="27" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        999 購入
+H00001630
+ナフトール、イオーオーデ</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>8.3334</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>33.40
 枚</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="18" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="19" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="21" t="n"/>
+      <c r="O13" s="13" t="n"/>
+      <c r="P13" s="11" t="n"/>
+      <c r="Q13" s="13" t="n"/>
+      <c r="R13" s="11" t="n"/>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="12" t="n"/>
+      <c r="U13" s="12" t="n"/>
+      <c r="V13" s="13" t="n"/>
+      <c r="W13" s="12" t="n"/>
+      <c r="X13" s="13" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="19" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="21" t="n"/>
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="11" t="n"/>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="11" t="n"/>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="11" t="n"/>
+      <c r="S14" s="12" t="n"/>
+      <c r="T14" s="12" t="n"/>
+      <c r="U14" s="12" t="n"/>
+      <c r="V14" s="13" t="n"/>
+      <c r="W14" s="12" t="n"/>
+      <c r="X14" s="13" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="19" t="n"/>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-      <c r="L15" s="21" t="n"/>
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="13" t="n"/>
+      <c r="P15" s="11" t="n"/>
+      <c r="Q15" s="13" t="n"/>
+      <c r="R15" s="11" t="n"/>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="12" t="n"/>
+      <c r="U15" s="12" t="n"/>
+      <c r="V15" s="13" t="n"/>
+      <c r="W15" s="12" t="n"/>
+      <c r="X15" s="13" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="19" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="20" t="n"/>
-      <c r="L16" s="21" t="n"/>
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="11" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="11" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="11" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="12" t="n"/>
+      <c r="U16" s="12" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="13" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="19" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
-      <c r="L17" s="21" t="n"/>
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="11" t="n"/>
+      <c r="Q17" s="13" t="n"/>
+      <c r="R17" s="11" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="12" t="n"/>
+      <c r="V17" s="13" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="13" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="19" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="20" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="20" t="n"/>
-      <c r="L18" s="21" t="n"/>
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="11" t="n"/>
+      <c r="O18" s="13" t="n"/>
+      <c r="P18" s="11" t="n"/>
+      <c r="Q18" s="13" t="n"/>
+      <c r="R18" s="11" t="n"/>
+      <c r="S18" s="12" t="n"/>
+      <c r="T18" s="12" t="n"/>
+      <c r="U18" s="12" t="n"/>
+      <c r="V18" s="13" t="n"/>
+      <c r="W18" s="12" t="n"/>
+      <c r="X18" s="13" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="19" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="21" t="n"/>
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="11" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="12" t="n"/>
+      <c r="U19" s="12" t="n"/>
+      <c r="V19" s="13" t="n"/>
+      <c r="W19" s="12" t="n"/>
+      <c r="X19" s="13" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="20" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="21" t="n"/>
+      <c r="A20" s="29" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="11" t="n"/>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="11" t="n"/>
+      <c r="Q20" s="13" t="n"/>
+      <c r="R20" s="11" t="n"/>
+      <c r="S20" s="12" t="n"/>
+      <c r="T20" s="12" t="n"/>
+      <c r="U20" s="12" t="n"/>
+      <c r="V20" s="13" t="n"/>
+      <c r="W20" s="12" t="n"/>
+      <c r="X20" s="13" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="19" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-      <c r="L21" s="21" t="n"/>
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="13" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="13" t="n"/>
+      <c r="R21" s="11" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="12" t="n"/>
+      <c r="U21" s="12" t="n"/>
+      <c r="V21" s="13" t="n"/>
+      <c r="W21" s="12" t="n"/>
+      <c r="X21" s="13" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-      <c r="L22" s="21" t="n"/>
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="O22" s="13" t="n"/>
+      <c r="P22" s="11" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="11" t="n"/>
+      <c r="S22" s="12" t="n"/>
+      <c r="T22" s="12" t="n"/>
+      <c r="U22" s="12" t="n"/>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="12" t="n"/>
+      <c r="X22" s="13" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="19" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="21" t="n"/>
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="13" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="13" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="13" t="n"/>
+      <c r="R23" s="11" t="n"/>
+      <c r="S23" s="12" t="n"/>
+      <c r="T23" s="12" t="n"/>
+      <c r="U23" s="12" t="n"/>
+      <c r="V23" s="13" t="n"/>
+      <c r="W23" s="12" t="n"/>
+      <c r="X23" s="13" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="19" t="n"/>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="21" t="n"/>
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="11" t="n"/>
+      <c r="O24" s="13" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="11" t="n"/>
+      <c r="S24" s="12" t="n"/>
+      <c r="T24" s="12" t="n"/>
+      <c r="U24" s="12" t="n"/>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="12" t="n"/>
+      <c r="X24" s="13" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="19" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="20" t="n"/>
-      <c r="L25" s="21" t="n"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="23" t="n"/>
-      <c r="H26" s="23" t="n"/>
-      <c r="I26" s="23" t="n"/>
-      <c r="J26" s="23" t="n"/>
-      <c r="K26" s="23" t="n"/>
-      <c r="L26" s="24" t="n"/>
+      <c r="A25" s="29" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="13" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="13" t="n"/>
+      <c r="R25" s="11" t="n"/>
+      <c r="S25" s="12" t="n"/>
+      <c r="T25" s="12" t="n"/>
+      <c r="U25" s="12" t="n"/>
+      <c r="V25" s="13" t="n"/>
+      <c r="W25" s="12" t="n"/>
+      <c r="X25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="11" t="n"/>
+      <c r="O26" s="13" t="n"/>
+      <c r="P26" s="11" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="11" t="n"/>
+      <c r="S26" s="12" t="n"/>
+      <c r="T26" s="12" t="n"/>
+      <c r="U26" s="12" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="12" t="n"/>
+      <c r="X26" s="13" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="13" t="n"/>
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="13" t="n"/>
+      <c r="R27" s="11" t="n"/>
+      <c r="S27" s="12" t="n"/>
+      <c r="T27" s="12" t="n"/>
+      <c r="U27" s="12" t="n"/>
+      <c r="V27" s="13" t="n"/>
+      <c r="W27" s="12" t="n"/>
+      <c r="X27" s="13" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="11" t="n"/>
+      <c r="O28" s="13" t="n"/>
+      <c r="P28" s="11" t="n"/>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="11" t="n"/>
+      <c r="S28" s="12" t="n"/>
+      <c r="T28" s="12" t="n"/>
+      <c r="U28" s="12" t="n"/>
+      <c r="V28" s="13" t="n"/>
+      <c r="W28" s="12" t="n"/>
+      <c r="X28" s="13" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="29" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="13" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="13" t="n"/>
+      <c r="R29" s="11" t="n"/>
+      <c r="S29" s="12" t="n"/>
+      <c r="T29" s="12" t="n"/>
+      <c r="U29" s="12" t="n"/>
+      <c r="V29" s="13" t="n"/>
+      <c r="W29" s="12" t="n"/>
+      <c r="X29" s="13" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="11" t="n"/>
+      <c r="O30" s="13" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="13" t="n"/>
+      <c r="R30" s="11" t="n"/>
+      <c r="S30" s="12" t="n"/>
+      <c r="T30" s="12" t="n"/>
+      <c r="U30" s="12" t="n"/>
+      <c r="V30" s="13" t="n"/>
+      <c r="W30" s="12" t="n"/>
+      <c r="X30" s="13" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="13" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="13" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="13" t="n"/>
+      <c r="R31" s="11" t="n"/>
+      <c r="S31" s="12" t="n"/>
+      <c r="T31" s="12" t="n"/>
+      <c r="U31" s="12" t="n"/>
+      <c r="V31" s="13" t="n"/>
+      <c r="W31" s="12" t="n"/>
+      <c r="X31" s="13" t="n"/>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>調合票</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="31" t="n"/>
+      <c r="K32" s="31" t="n"/>
+      <c r="L32" s="31" t="n"/>
+      <c r="M32" s="31" t="n"/>
+      <c r="N32" s="31" t="n"/>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="31" t="n"/>
+      <c r="Q32" s="31" t="n"/>
+      <c r="R32" s="31" t="n"/>
+      <c r="S32" s="31" t="n"/>
+      <c r="T32" s="31" t="n"/>
+      <c r="U32" s="31" t="n"/>
+      <c r="V32" s="31" t="n"/>
+      <c r="W32" s="31" t="n"/>
+      <c r="X32" s="32" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A25:F25"/>
+  <mergeCells count="157">
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="R16:V16"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="R8:X8"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A10:K11"/>
+    <mergeCell ref="A32:X32"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="W10:X11"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="D7:N7"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="R14:V14"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="L10:M11"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="R27:V27"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R7:X7"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="R29:V29"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="R13:V13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="R31:V31"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="R5:X5"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="R15:V15"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="R26:V26"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="R10:V11"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A9:X9"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="O2:X2"/>
+    <mergeCell ref="R28:V28"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R30:V30"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R12:V12"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="R6:X6"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="D8:N8"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -810,7 +810,7 @@
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>S000002 製造１課　倉庫</t>
+          <t>500000200 製造１課　倉庫</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -832,7 +832,7 @@
       <c r="Q4" s="10" t="n"/>
       <c r="R4" s="9" t="inlineStr">
         <is>
-          <t>S000002 製造１課　倉庫</t>
+          <t>500000200 製造１課　倉庫</t>
         </is>
       </c>
       <c r="S4" s="9" t="n"/>
@@ -880,7 +880,11 @@
       </c>
       <c r="P5" s="12" t="n"/>
       <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>400.72 kg</t>
+        </is>
+      </c>
       <c r="S5" s="12" t="n"/>
       <c r="T5" s="12" t="n"/>
       <c r="U5" s="12" t="n"/>
@@ -962,7 +966,7 @@
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>S000002 製造１課　倉庫</t>
+          <t>500000200　製造１課　倉庫</t>
         </is>
       </c>
       <c r="S7" s="12" t="n"/>
@@ -1155,8 +1159,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">        999 購入
-H00001630
+          <t>H0001630        999 購入
 ナフトール、イオーオーデ</t>
         </is>
       </c>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -27,16 +27,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="12"/>
     </font>
     <font>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00000000"/>
       <sz val="22"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -673,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7265625" customWidth="1" min="1" max="1"/>
@@ -742,7 +746,7 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0000056473</t>
+          <t>0000056473 1</t>
         </is>
       </c>
       <c r="E2" s="5" t="n"/>
@@ -757,7 +761,7 @@
       <c r="J2" s="6" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2018/12/14</t>
+          <t>2018/12/05</t>
         </is>
       </c>
       <c r="L2" s="5" t="n"/>
@@ -810,7 +814,7 @@
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>500000200 製造１課　倉庫</t>
+          <t>S00000200 製造1課 倉庫</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -832,7 +836,7 @@
       <c r="Q4" s="10" t="n"/>
       <c r="R4" s="9" t="inlineStr">
         <is>
-          <t>500000200 製造１課　倉庫</t>
+          <t>2018/12/14</t>
         </is>
       </c>
       <c r="S4" s="9" t="n"/>
@@ -902,7 +906,7 @@
       <c r="C6" s="13" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>ネイジーマキアップ サテン(37才混血)連絡品</t>
+          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
@@ -944,7 +948,7 @@
       <c r="C7" s="13" t="n"/>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>30　噴霧</t>
+          <t>30 噴霧</t>
         </is>
       </c>
       <c r="E7" s="12" t="n"/>
@@ -966,7 +970,7 @@
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>500000200　製造１課　倉庫</t>
+          <t>S00000200 製造1課 倉庫</t>
         </is>
       </c>
       <c r="S7" s="12" t="n"/>
@@ -1120,7 +1124,7 @@
       <c r="A12" s="25" t="inlineStr">
         <is>
           <t>HA0002610        100 仕込
-ネイジーマキアップ サテン(37才混血)連絡品</t>
+クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
         </is>
       </c>
       <c r="B12" s="26" t="n"/>
@@ -1159,8 +1163,8 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>H0001630        999 購入
-ナフトール、イオーオーデ</t>
+          <t>H00001630        999 購入
+クラフト袋L イージーオープン</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
@@ -1612,90 +1616,38 @@
       <c r="W29" s="12" t="n"/>
       <c r="X29" s="13" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="13" t="n"/>
-      <c r="N30" s="11" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="11" t="n"/>
-      <c r="S30" s="12" t="n"/>
-      <c r="T30" s="12" t="n"/>
-      <c r="U30" s="12" t="n"/>
-      <c r="V30" s="13" t="n"/>
-      <c r="W30" s="12" t="n"/>
-      <c r="X30" s="13" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="13" t="n"/>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="13" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="13" t="n"/>
-      <c r="R31" s="11" t="n"/>
-      <c r="S31" s="12" t="n"/>
-      <c r="T31" s="12" t="n"/>
-      <c r="U31" s="12" t="n"/>
-      <c r="V31" s="13" t="n"/>
-      <c r="W31" s="12" t="n"/>
-      <c r="X31" s="13" t="n"/>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>調合票</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
-      <c r="Q32" s="31" t="n"/>
-      <c r="R32" s="31" t="n"/>
-      <c r="S32" s="31" t="n"/>
-      <c r="T32" s="31" t="n"/>
-      <c r="U32" s="31" t="n"/>
-      <c r="V32" s="31" t="n"/>
-      <c r="W32" s="31" t="n"/>
-      <c r="X32" s="32" t="n"/>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="31" t="n"/>
+      <c r="O30" s="31" t="n"/>
+      <c r="P30" s="31" t="n"/>
+      <c r="Q30" s="31" t="n"/>
+      <c r="R30" s="31" t="n"/>
+      <c r="S30" s="31" t="n"/>
+      <c r="T30" s="31" t="n"/>
+      <c r="U30" s="31" t="n"/>
+      <c r="V30" s="31" t="n"/>
+      <c r="W30" s="31" t="n"/>
+      <c r="X30" s="32" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="157">
+  <mergeCells count="145">
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="P20:Q20"/>
@@ -1719,7 +1671,6 @@
     <mergeCell ref="R8:X8"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A10:K11"/>
-    <mergeCell ref="A32:X32"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="W10:X11"/>
     <mergeCell ref="N14:O14"/>
@@ -1732,9 +1683,7 @@
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="D4:N4"/>
     <mergeCell ref="R22:V22"/>
-    <mergeCell ref="L31:M31"/>
     <mergeCell ref="A17:K17"/>
-    <mergeCell ref="N31:O31"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="N15:O15"/>
@@ -1752,7 +1701,6 @@
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="O5:Q5"/>
     <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="A30:K30"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="L10:M11"/>
@@ -1762,7 +1710,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="R27:V27"/>
-    <mergeCell ref="L30:M30"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="L20:M20"/>
@@ -1775,9 +1722,8 @@
     <mergeCell ref="R17:V17"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="W27:X27"/>
-    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="A30:X30"/>
     <mergeCell ref="W17:X17"/>
-    <mergeCell ref="P30:Q30"/>
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="W19:X19"/>
@@ -1789,8 +1735,6 @@
     <mergeCell ref="R13:V13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="R31:V31"/>
     <mergeCell ref="W20:X20"/>
     <mergeCell ref="R5:X5"/>
     <mergeCell ref="L24:M24"/>
@@ -1801,7 +1745,6 @@
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="W22:X22"/>
-    <mergeCell ref="W31:X31"/>
     <mergeCell ref="N17:O17"/>
     <mergeCell ref="R21:V21"/>
     <mergeCell ref="L26:M26"/>
@@ -1826,11 +1769,9 @@
     <mergeCell ref="R19:V19"/>
     <mergeCell ref="O2:X2"/>
     <mergeCell ref="R28:V28"/>
-    <mergeCell ref="P31:Q31"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R30:V30"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="L15:M15"/>
@@ -1852,7 +1793,6 @@
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="R18:V18"/>
     <mergeCell ref="W13:X13"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="製造指図書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +233,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -746,29 +749,33 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0000056473 1</t>
+          <t>0000056473</t>
         </is>
       </c>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>2018/12/05</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n"/>
       <c r="M2" s="5" t="n"/>
-      <c r="N2" s="6" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="4" t="n"/>
       <c r="Q2" s="5" t="n"/>
       <c r="R2" s="5" t="n"/>
       <c r="S2" s="5" t="n"/>
@@ -779,872 +786,872 @@
       <c r="X2" s="6" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
-      <c r="M3" s="7" t="n"/>
-      <c r="N3" s="7" t="n"/>
-      <c r="O3" s="7" t="n"/>
-      <c r="P3" s="7" t="n"/>
-      <c r="Q3" s="7" t="n"/>
-      <c r="R3" s="7" t="n"/>
-      <c r="S3" s="7" t="n"/>
-      <c r="T3" s="7" t="n"/>
-      <c r="U3" s="7" t="n"/>
-      <c r="V3" s="7" t="n"/>
-      <c r="W3" s="7" t="n"/>
-      <c r="X3" s="7" t="n"/>
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="n"/>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="8" t="n"/>
+      <c r="T3" s="8" t="n"/>
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="8" t="n"/>
+      <c r="W3" s="8" t="n"/>
+      <c r="X3" s="8" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>手配先</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>S00000200 製造1課 倉庫</t>
         </is>
       </c>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>手配調整期</t>
         </is>
       </c>
-      <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="9" t="inlineStr">
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>2018/12/14</t>
         </is>
       </c>
-      <c r="S4" s="9" t="n"/>
-      <c r="T4" s="9" t="n"/>
-      <c r="U4" s="9" t="n"/>
-      <c r="V4" s="9" t="n"/>
-      <c r="W4" s="9" t="n"/>
-      <c r="X4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="11" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>品目CD</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>HA0002610</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>工順</t>
         </is>
       </c>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>発注手配数</t>
         </is>
       </c>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="12" t="inlineStr">
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>400.72 kg</t>
         </is>
       </c>
-      <c r="S5" s="12" t="n"/>
-      <c r="T5" s="12" t="n"/>
-      <c r="U5" s="12" t="n"/>
-      <c r="V5" s="12" t="n"/>
-      <c r="W5" s="12" t="n"/>
-      <c r="X5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="14" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>品目名</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>製番</t>
         </is>
       </c>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="12" t="inlineStr">
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>0000051090</t>
         </is>
       </c>
-      <c r="S6" s="12" t="n"/>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="12" t="n"/>
-      <c r="V6" s="12" t="n"/>
-      <c r="W6" s="12" t="n"/>
-      <c r="X6" s="13" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="14" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>手配内容</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>30 噴霧</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="14" t="n"/>
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>完成入庫</t>
         </is>
       </c>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="12" t="inlineStr">
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>S00000200 製造1課 倉庫</t>
         </is>
       </c>
-      <c r="S7" s="12" t="n"/>
-      <c r="T7" s="12" t="n"/>
-      <c r="U7" s="12" t="n"/>
-      <c r="V7" s="12" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="13" t="n"/>
+      <c r="S7" s="13" t="n"/>
+      <c r="T7" s="13" t="n"/>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="n"/>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="14" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>ロットNo.</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="12" t="inlineStr">
         <is>
           <t>完成日</t>
         </is>
       </c>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="12" t="n"/>
-      <c r="S8" s="12" t="n"/>
-      <c r="T8" s="12" t="n"/>
-      <c r="U8" s="12" t="n"/>
-      <c r="V8" s="12" t="n"/>
-      <c r="W8" s="12" t="n"/>
-      <c r="X8" s="13" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="14" t="n"/>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>調合票</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="14" t="n"/>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="14" t="n"/>
-      <c r="S9" s="14" t="n"/>
-      <c r="T9" s="14" t="n"/>
-      <c r="U9" s="14" t="n"/>
-      <c r="V9" s="14" t="n"/>
-      <c r="W9" s="14" t="n"/>
-      <c r="X9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="15" t="n"/>
+      <c r="N9" s="15" t="n"/>
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="15" t="n"/>
+      <c r="Q9" s="15" t="n"/>
+      <c r="R9" s="15" t="n"/>
+      <c r="S9" s="15" t="n"/>
+      <c r="T9" s="15" t="n"/>
+      <c r="U9" s="15" t="n"/>
+      <c r="V9" s="15" t="n"/>
+      <c r="W9" s="15" t="n"/>
+      <c r="X9" s="15" t="n"/>
     </row>
     <row r="10" ht="14.5" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>成分名</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="17" t="n"/>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>原単位</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="19" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
-      <c r="O10" s="17" t="n"/>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="O10" s="18" t="n"/>
+      <c r="P10" s="19" t="inlineStr">
         <is>
           <t>検量者</t>
         </is>
       </c>
-      <c r="Q10" s="17" t="n"/>
-      <c r="R10" s="18" t="inlineStr">
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="19" t="inlineStr">
         <is>
           <t>原料ロット</t>
         </is>
       </c>
-      <c r="S10" s="16" t="n"/>
-      <c r="T10" s="16" t="n"/>
-      <c r="U10" s="16" t="n"/>
-      <c r="V10" s="17" t="n"/>
-      <c r="W10" s="16" t="inlineStr">
+      <c r="S10" s="17" t="n"/>
+      <c r="T10" s="17" t="n"/>
+      <c r="U10" s="17" t="n"/>
+      <c r="V10" s="18" t="n"/>
+      <c r="W10" s="17" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="X10" s="17" t="n"/>
+      <c r="X10" s="18" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="19" t="n"/>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="22" t="n"/>
-      <c r="M11" s="23" t="n"/>
-      <c r="N11" s="22" t="n"/>
-      <c r="O11" s="23" t="n"/>
-      <c r="P11" s="22" t="n"/>
-      <c r="Q11" s="23" t="n"/>
-      <c r="R11" s="24" t="n"/>
-      <c r="S11" s="20" t="n"/>
-      <c r="T11" s="20" t="n"/>
-      <c r="U11" s="20" t="n"/>
-      <c r="V11" s="21" t="n"/>
-      <c r="W11" s="20" t="n"/>
-      <c r="X11" s="21" t="n"/>
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="24" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="24" t="n"/>
+      <c r="R11" s="25" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="22" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>HA0002610        100 仕込
-クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="28" t="inlineStr">
+クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="27" t="n"/>
+      <c r="J12" s="27" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="29" t="inlineStr">
         <is>
           <t>100.0000</t>
         </is>
       </c>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="28" t="inlineStr">
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="29" t="inlineStr">
         <is>
           <t>400.72
 kg</t>
         </is>
       </c>
-      <c r="O12" s="27" t="n"/>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="27" t="n"/>
-      <c r="R12" s="28" t="n"/>
-      <c r="S12" s="26" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="27" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="27" t="n"/>
+      <c r="O12" s="28" t="n"/>
+      <c r="P12" s="29" t="n"/>
+      <c r="Q12" s="28" t="n"/>
+      <c r="R12" s="29" t="n"/>
+      <c r="S12" s="27" t="n"/>
+      <c r="T12" s="27" t="n"/>
+      <c r="U12" s="27" t="n"/>
+      <c r="V12" s="28" t="n"/>
+      <c r="W12" s="27" t="n"/>
+      <c r="X12" s="28" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>H00001630        999 購入
 クラフト袋L イージーオープン</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>8.3334</t>
         </is>
       </c>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>33.40
 枚</t>
         </is>
       </c>
-      <c r="O13" s="13" t="n"/>
-      <c r="P13" s="11" t="n"/>
-      <c r="Q13" s="13" t="n"/>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="12" t="n"/>
-      <c r="T13" s="12" t="n"/>
-      <c r="U13" s="12" t="n"/>
-      <c r="V13" s="13" t="n"/>
-      <c r="W13" s="12" t="n"/>
-      <c r="X13" s="13" t="n"/>
+      <c r="O13" s="14" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="13" t="n"/>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="14" t="n"/>
+      <c r="W13" s="13" t="n"/>
+      <c r="X13" s="14" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="29" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="11" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="11" t="n"/>
-      <c r="S14" s="12" t="n"/>
-      <c r="T14" s="12" t="n"/>
-      <c r="U14" s="12" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="12" t="n"/>
-      <c r="X14" s="13" t="n"/>
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="14" t="n"/>
+      <c r="P14" s="12" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="12" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="13" t="n"/>
+      <c r="V14" s="14" t="n"/>
+      <c r="W14" s="13" t="n"/>
+      <c r="X14" s="14" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="13" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="13" t="n"/>
-      <c r="R15" s="11" t="n"/>
-      <c r="S15" s="12" t="n"/>
-      <c r="T15" s="12" t="n"/>
-      <c r="U15" s="12" t="n"/>
-      <c r="V15" s="13" t="n"/>
-      <c r="W15" s="12" t="n"/>
-      <c r="X15" s="13" t="n"/>
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="14" t="n"/>
+      <c r="P15" s="12" t="n"/>
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="12" t="n"/>
+      <c r="S15" s="13" t="n"/>
+      <c r="T15" s="13" t="n"/>
+      <c r="U15" s="13" t="n"/>
+      <c r="V15" s="14" t="n"/>
+      <c r="W15" s="13" t="n"/>
+      <c r="X15" s="14" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="11" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="11" t="n"/>
-      <c r="S16" s="12" t="n"/>
-      <c r="T16" s="12" t="n"/>
-      <c r="U16" s="12" t="n"/>
-      <c r="V16" s="13" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="13" t="n"/>
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="14" t="n"/>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="14" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="11" t="n"/>
-      <c r="Q17" s="13" t="n"/>
-      <c r="R17" s="11" t="n"/>
-      <c r="S17" s="12" t="n"/>
-      <c r="T17" s="12" t="n"/>
-      <c r="U17" s="12" t="n"/>
-      <c r="V17" s="13" t="n"/>
-      <c r="W17" s="12" t="n"/>
-      <c r="X17" s="13" t="n"/>
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="13" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="13" t="n"/>
+      <c r="V17" s="14" t="n"/>
+      <c r="W17" s="13" t="n"/>
+      <c r="X17" s="14" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="13" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="11" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="11" t="n"/>
-      <c r="S18" s="12" t="n"/>
-      <c r="T18" s="12" t="n"/>
-      <c r="U18" s="12" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="12" t="n"/>
-      <c r="X18" s="13" t="n"/>
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="13" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="12" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="12" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="13" t="n"/>
+      <c r="V18" s="14" t="n"/>
+      <c r="W18" s="13" t="n"/>
+      <c r="X18" s="14" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="12" t="n"/>
-      <c r="T19" s="12" t="n"/>
-      <c r="U19" s="12" t="n"/>
-      <c r="V19" s="13" t="n"/>
-      <c r="W19" s="12" t="n"/>
-      <c r="X19" s="13" t="n"/>
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="14" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="13" t="n"/>
+      <c r="V19" s="14" t="n"/>
+      <c r="W19" s="13" t="n"/>
+      <c r="X19" s="14" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="29" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="11" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="11" t="n"/>
-      <c r="S20" s="12" t="n"/>
-      <c r="T20" s="12" t="n"/>
-      <c r="U20" s="12" t="n"/>
-      <c r="V20" s="13" t="n"/>
-      <c r="W20" s="12" t="n"/>
-      <c r="X20" s="13" t="n"/>
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="13" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="12" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+      <c r="R20" s="12" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="13" t="n"/>
+      <c r="V20" s="14" t="n"/>
+      <c r="W20" s="13" t="n"/>
+      <c r="X20" s="14" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="13" t="n"/>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="13" t="n"/>
-      <c r="R21" s="11" t="n"/>
-      <c r="S21" s="12" t="n"/>
-      <c r="T21" s="12" t="n"/>
-      <c r="U21" s="12" t="n"/>
-      <c r="V21" s="13" t="n"/>
-      <c r="W21" s="12" t="n"/>
-      <c r="X21" s="13" t="n"/>
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="14" t="n"/>
+      <c r="P21" s="12" t="n"/>
+      <c r="Q21" s="14" t="n"/>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="13" t="n"/>
+      <c r="V21" s="14" t="n"/>
+      <c r="W21" s="13" t="n"/>
+      <c r="X21" s="14" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="11" t="n"/>
-      <c r="M22" s="13" t="n"/>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="11" t="n"/>
-      <c r="S22" s="12" t="n"/>
-      <c r="T22" s="12" t="n"/>
-      <c r="U22" s="12" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="12" t="n"/>
-      <c r="X22" s="13" t="n"/>
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="13" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="14" t="n"/>
+      <c r="P22" s="12" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="12" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="14" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="14" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="13" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="13" t="n"/>
-      <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="13" t="n"/>
-      <c r="R23" s="11" t="n"/>
-      <c r="S23" s="12" t="n"/>
-      <c r="T23" s="12" t="n"/>
-      <c r="U23" s="12" t="n"/>
-      <c r="V23" s="13" t="n"/>
-      <c r="W23" s="12" t="n"/>
-      <c r="X23" s="13" t="n"/>
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="14" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="14" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="14" t="n"/>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="13" t="n"/>
+      <c r="U23" s="13" t="n"/>
+      <c r="V23" s="14" t="n"/>
+      <c r="W23" s="13" t="n"/>
+      <c r="X23" s="14" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="13" t="n"/>
-      <c r="P24" s="11" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="11" t="n"/>
-      <c r="S24" s="12" t="n"/>
-      <c r="T24" s="12" t="n"/>
-      <c r="U24" s="12" t="n"/>
-      <c r="V24" s="13" t="n"/>
-      <c r="W24" s="12" t="n"/>
-      <c r="X24" s="13" t="n"/>
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="13" t="n"/>
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="14" t="n"/>
+      <c r="P24" s="12" t="n"/>
+      <c r="Q24" s="14" t="n"/>
+      <c r="R24" s="12" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="14" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="14" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="13" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="13" t="n"/>
-      <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="13" t="n"/>
-      <c r="R25" s="11" t="n"/>
-      <c r="S25" s="12" t="n"/>
-      <c r="T25" s="12" t="n"/>
-      <c r="U25" s="12" t="n"/>
-      <c r="V25" s="13" t="n"/>
-      <c r="W25" s="12" t="n"/>
-      <c r="X25" s="13" t="n"/>
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="14" t="n"/>
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="12" t="n"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="13" t="n"/>
+      <c r="U25" s="13" t="n"/>
+      <c r="V25" s="14" t="n"/>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="14" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="11" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="11" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="11" t="n"/>
-      <c r="S26" s="12" t="n"/>
-      <c r="T26" s="12" t="n"/>
-      <c r="U26" s="12" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="12" t="n"/>
-      <c r="X26" s="13" t="n"/>
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="14" t="n"/>
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="14" t="n"/>
+      <c r="R26" s="12" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="14" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="14" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="13" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="12" t="n"/>
-      <c r="T27" s="12" t="n"/>
-      <c r="U27" s="12" t="n"/>
-      <c r="V27" s="13" t="n"/>
-      <c r="W27" s="12" t="n"/>
-      <c r="X27" s="13" t="n"/>
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="14" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="14" t="n"/>
+      <c r="P27" s="12" t="n"/>
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="12" t="n"/>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="13" t="n"/>
+      <c r="U27" s="13" t="n"/>
+      <c r="V27" s="14" t="n"/>
+      <c r="W27" s="13" t="n"/>
+      <c r="X27" s="14" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="11" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="11" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="11" t="n"/>
-      <c r="S28" s="12" t="n"/>
-      <c r="T28" s="12" t="n"/>
-      <c r="U28" s="12" t="n"/>
-      <c r="V28" s="13" t="n"/>
-      <c r="W28" s="12" t="n"/>
-      <c r="X28" s="13" t="n"/>
+      <c r="A28" s="30" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="14" t="n"/>
+      <c r="P28" s="12" t="n"/>
+      <c r="Q28" s="14" t="n"/>
+      <c r="R28" s="12" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="14" t="n"/>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="14" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="13" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="13" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="13" t="n"/>
-      <c r="R29" s="11" t="n"/>
-      <c r="S29" s="12" t="n"/>
-      <c r="T29" s="12" t="n"/>
-      <c r="U29" s="12" t="n"/>
-      <c r="V29" s="13" t="n"/>
-      <c r="W29" s="12" t="n"/>
-      <c r="X29" s="13" t="n"/>
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="13" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="14" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="14" t="n"/>
+      <c r="P29" s="12" t="n"/>
+      <c r="Q29" s="14" t="n"/>
+      <c r="R29" s="12" t="n"/>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="13" t="n"/>
+      <c r="U29" s="13" t="n"/>
+      <c r="V29" s="14" t="n"/>
+      <c r="W29" s="13" t="n"/>
+      <c r="X29" s="14" t="n"/>
     </row>
     <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-      <c r="U30" s="31" t="n"/>
-      <c r="V30" s="31" t="n"/>
-      <c r="W30" s="31" t="n"/>
-      <c r="X30" s="32" t="n"/>
+      <c r="B30" s="32" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="32" t="n"/>
+      <c r="I30" s="32" t="n"/>
+      <c r="J30" s="32" t="n"/>
+      <c r="K30" s="32" t="n"/>
+      <c r="L30" s="32" t="n"/>
+      <c r="M30" s="32" t="n"/>
+      <c r="N30" s="32" t="n"/>
+      <c r="O30" s="32" t="n"/>
+      <c r="P30" s="32" t="n"/>
+      <c r="Q30" s="32" t="n"/>
+      <c r="R30" s="32" t="n"/>
+      <c r="S30" s="32" t="n"/>
+      <c r="T30" s="32" t="n"/>
+      <c r="U30" s="32" t="n"/>
+      <c r="V30" s="32" t="n"/>
+      <c r="W30" s="32" t="n"/>
+      <c r="X30" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="145">
@@ -1666,7 +1673,6 @@
     <mergeCell ref="W26:X26"/>
     <mergeCell ref="N12:O12"/>
     <mergeCell ref="R16:V16"/>
-    <mergeCell ref="D2:H2"/>
     <mergeCell ref="R25:V25"/>
     <mergeCell ref="R8:X8"/>
     <mergeCell ref="A16:K16"/>
@@ -1694,13 +1700,13 @@
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="A28:K28"/>
     <mergeCell ref="W14:X14"/>
-    <mergeCell ref="K2:N2"/>
     <mergeCell ref="W28:X28"/>
     <mergeCell ref="R14:V14"/>
     <mergeCell ref="R23:V23"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="O5:Q5"/>
     <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P2:X2"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="L10:M11"/>
@@ -1708,6 +1714,7 @@
     <mergeCell ref="N10:O11"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="L2:O2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="R27:V27"/>
     <mergeCell ref="W16:X16"/>
@@ -1727,7 +1734,6 @@
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="W19:X19"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="W25:X25"/>
     <mergeCell ref="R29:V29"/>
     <mergeCell ref="K5:L5"/>
@@ -1759,15 +1765,16 @@
     <mergeCell ref="N19:O19"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D2:G2"/>
     <mergeCell ref="R10:V11"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A9:X9"/>
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="P29:Q29"/>
     <mergeCell ref="R19:V19"/>
-    <mergeCell ref="O2:X2"/>
     <mergeCell ref="R28:V28"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="N21:O21"/>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -680,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7265625" customWidth="1" min="1" max="1"/>
@@ -749,17 +749,13 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0000056473</t>
+          <t>S000005473</t>
         </is>
       </c>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="6" t="n"/>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H2" s="7" t="n"/>
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -769,7 +765,7 @@
       <c r="K2" s="6" t="n"/>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2018/12/05</t>
+          <t>2018/12/06</t>
         </is>
       </c>
       <c r="M2" s="5" t="n"/>
@@ -821,7 +817,7 @@
       <c r="C4" s="11" t="n"/>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>S00000200 製造1課 倉庫</t>
+          <t>2号</t>
         </is>
       </c>
       <c r="E4" s="10" t="n"/>
@@ -841,11 +837,7 @@
       </c>
       <c r="P4" s="10" t="n"/>
       <c r="Q4" s="11" t="n"/>
-      <c r="R4" s="10" t="inlineStr">
-        <is>
-          <t>2018/12/14</t>
-        </is>
-      </c>
+      <c r="R4" s="10" t="n"/>
       <c r="S4" s="10" t="n"/>
       <c r="T4" s="10" t="n"/>
       <c r="U4" s="10" t="n"/>
@@ -863,7 +855,7 @@
       <c r="C5" s="14" t="n"/>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>HA0002610</t>
+          <t>HA00002610 混合1番 煮 業</t>
         </is>
       </c>
       <c r="E5" s="13" t="n"/>
@@ -891,11 +883,7 @@
       </c>
       <c r="P5" s="13" t="n"/>
       <c r="Q5" s="14" t="n"/>
-      <c r="R5" s="13" t="inlineStr">
-        <is>
-          <t>400.72 kg</t>
-        </is>
-      </c>
+      <c r="R5" s="13" t="n"/>
       <c r="S5" s="13" t="n"/>
       <c r="T5" s="13" t="n"/>
       <c r="U5" s="13" t="n"/>
@@ -913,7 +901,7 @@
       <c r="C6" s="14" t="n"/>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
+          <t>ドレッシングタイプ調味料(サラダ用/業務用/着色料不使用)</t>
         </is>
       </c>
       <c r="E6" s="13" t="n"/>
@@ -933,11 +921,7 @@
       </c>
       <c r="P6" s="13" t="n"/>
       <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="13" t="inlineStr">
-        <is>
-          <t>0000051090</t>
-        </is>
-      </c>
+      <c r="R6" s="13" t="n"/>
       <c r="S6" s="13" t="n"/>
       <c r="T6" s="13" t="n"/>
       <c r="U6" s="13" t="n"/>
@@ -955,7 +939,7 @@
       <c r="C7" s="14" t="n"/>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>30 噴霧</t>
+          <t>S00000200 混合1番 煮 業</t>
         </is>
       </c>
       <c r="E7" s="13" t="n"/>
@@ -975,11 +959,7 @@
       </c>
       <c r="P7" s="13" t="n"/>
       <c r="Q7" s="14" t="n"/>
-      <c r="R7" s="13" t="inlineStr">
-        <is>
-          <t>S00000200 製造1課 倉庫</t>
-        </is>
-      </c>
+      <c r="R7" s="13" t="n"/>
       <c r="S7" s="13" t="n"/>
       <c r="T7" s="13" t="n"/>
       <c r="U7" s="13" t="n"/>
@@ -1128,12 +1108,7 @@
       <c r="X11" s="22" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>HA0002610        100 仕込
-クレイジーマックスプロテイン(カフェオレ風味)造粒品</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="n"/>
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="27" t="n"/>
       <c r="D12" s="27" t="n"/>
@@ -1144,16 +1119,12 @@
       <c r="I12" s="27" t="n"/>
       <c r="J12" s="27" t="n"/>
       <c r="K12" s="28" t="n"/>
-      <c r="L12" s="29" t="inlineStr">
-        <is>
-          <t>100.0000</t>
-        </is>
-      </c>
+      <c r="L12" s="29" t="n"/>
       <c r="M12" s="28" t="n"/>
       <c r="N12" s="29" t="inlineStr">
         <is>
-          <t>400.72
-kg</t>
+          <t>100.0000
+8.3334</t>
         </is>
       </c>
       <c r="O12" s="28" t="n"/>
@@ -1168,12 +1139,7 @@
       <c r="X12" s="28" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>H00001630        999 購入
-クラフト袋L イージーオープン</t>
-        </is>
-      </c>
+      <c r="A13" s="30" t="n"/>
       <c r="B13" s="13" t="n"/>
       <c r="C13" s="13" t="n"/>
       <c r="D13" s="13" t="n"/>
@@ -1184,18 +1150,9 @@
       <c r="I13" s="13" t="n"/>
       <c r="J13" s="13" t="n"/>
       <c r="K13" s="14" t="n"/>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>8.3334</t>
-        </is>
-      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="14" t="n"/>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>33.40
-枚</t>
-        </is>
-      </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="14" t="n"/>
       <c r="P13" s="12" t="n"/>
       <c r="Q13" s="14" t="n"/>
@@ -1623,38 +1580,86 @@
       <c r="W29" s="13" t="n"/>
       <c r="X29" s="14" t="n"/>
     </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="31" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="32" t="n"/>
-      <c r="H30" s="32" t="n"/>
-      <c r="I30" s="32" t="n"/>
-      <c r="J30" s="32" t="n"/>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="32" t="n"/>
-      <c r="M30" s="32" t="n"/>
-      <c r="N30" s="32" t="n"/>
-      <c r="O30" s="32" t="n"/>
-      <c r="P30" s="32" t="n"/>
-      <c r="Q30" s="32" t="n"/>
-      <c r="R30" s="32" t="n"/>
-      <c r="S30" s="32" t="n"/>
-      <c r="T30" s="32" t="n"/>
-      <c r="U30" s="32" t="n"/>
-      <c r="V30" s="32" t="n"/>
-      <c r="W30" s="32" t="n"/>
-      <c r="X30" s="33" t="n"/>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="14" t="n"/>
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="14" t="n"/>
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="14" t="n"/>
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="14" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="14" t="n"/>
+      <c r="P31" s="12" t="n"/>
+      <c r="Q31" s="14" t="n"/>
+      <c r="R31" s="12" t="n"/>
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="13" t="n"/>
+      <c r="U31" s="13" t="n"/>
+      <c r="V31" s="14" t="n"/>
+      <c r="W31" s="13" t="n"/>
+      <c r="X31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="31" t="n"/>
+      <c r="B32" s="32" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="32" t="n"/>
+      <c r="E32" s="32" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="32" t="n"/>
+      <c r="H32" s="32" t="n"/>
+      <c r="I32" s="32" t="n"/>
+      <c r="J32" s="32" t="n"/>
+      <c r="K32" s="32" t="n"/>
+      <c r="L32" s="32" t="n"/>
+      <c r="M32" s="32" t="n"/>
+      <c r="N32" s="32" t="n"/>
+      <c r="O32" s="32" t="n"/>
+      <c r="P32" s="32" t="n"/>
+      <c r="Q32" s="32" t="n"/>
+      <c r="R32" s="32" t="n"/>
+      <c r="S32" s="32" t="n"/>
+      <c r="T32" s="32" t="n"/>
+      <c r="U32" s="32" t="n"/>
+      <c r="V32" s="32" t="n"/>
+      <c r="W32" s="32" t="n"/>
+      <c r="X32" s="33" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="145">
+  <mergeCells count="157">
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="P20:Q20"/>
@@ -1677,6 +1682,7 @@
     <mergeCell ref="R8:X8"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A10:K11"/>
+    <mergeCell ref="A32:X32"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="W10:X11"/>
     <mergeCell ref="N14:O14"/>
@@ -1689,7 +1695,9 @@
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="D4:N4"/>
     <mergeCell ref="R22:V22"/>
+    <mergeCell ref="L31:M31"/>
     <mergeCell ref="A17:K17"/>
+    <mergeCell ref="N31:O31"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="N15:O15"/>
@@ -1706,6 +1714,7 @@
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="O5:Q5"/>
     <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="P2:X2"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="N16:O16"/>
@@ -1717,6 +1726,7 @@
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="R27:V27"/>
+    <mergeCell ref="L30:M30"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="L20:M20"/>
@@ -1729,8 +1739,9 @@
     <mergeCell ref="R17:V17"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="W27:X27"/>
-    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="N30:O30"/>
     <mergeCell ref="W17:X17"/>
+    <mergeCell ref="P30:Q30"/>
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="W19:X19"/>
@@ -1741,6 +1752,8 @@
     <mergeCell ref="R13:V13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="R31:V31"/>
     <mergeCell ref="W20:X20"/>
     <mergeCell ref="R5:X5"/>
     <mergeCell ref="L24:M24"/>
@@ -1751,6 +1764,7 @@
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="W22:X22"/>
+    <mergeCell ref="W31:X31"/>
     <mergeCell ref="N17:O17"/>
     <mergeCell ref="R21:V21"/>
     <mergeCell ref="L26:M26"/>
@@ -1776,9 +1790,11 @@
     <mergeCell ref="P29:Q29"/>
     <mergeCell ref="R19:V19"/>
     <mergeCell ref="R28:V28"/>
+    <mergeCell ref="P31:Q31"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R30:V30"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="L15:M15"/>
@@ -1800,6 +1816,7 @@
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="R18:V18"/>
     <mergeCell ref="W13:X13"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/IMG_9689.xlsx
+++ b/output/IMG_9689.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,45 +26,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
       <b val="1"/>
-      <sz val="14"/>
     </font>
-    <font>
-      <name val="MS Gothic"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="MS Gothic"/>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="MS Gothic"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
+    <font/>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin"/>
@@ -100,57 +98,18 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -518,457 +477,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="2" customWidth="1" min="10" max="10"/>
+    <col width="7.75" customWidth="1" min="1" max="1"/>
+    <col width="13.33333333333333" customWidth="1" min="2" max="2"/>
+    <col width="13.33333333333333" customWidth="1" min="3" max="3"/>
+    <col width="13.33333333333333" customWidth="1" min="4" max="4"/>
+    <col width="13.33333333333333" customWidth="1" min="5" max="5"/>
+    <col width="13.33333333333333" customWidth="1" min="6" max="6"/>
+    <col width="13.33333333333333" customWidth="1" min="7" max="7"/>
+    <col width="13.33333333333333" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>製造指図書</t>
         </is>
       </c>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="5" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="6" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="7" t="inlineStr">
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>手配No.</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>手配先</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>手配納期</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>作成者</t>
         </is>
       </c>
-      <c r="J2" s="6" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>手配先</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>手配納期</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="8" t="n"/>
-      <c r="J3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="7" t="inlineStr">
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>品目CD</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>工順</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>発注手配数</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>品目名</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>製番</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>手配内容</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>完成入庫</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>ロットNo.</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>完成日</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>調合票</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="3" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>責任者</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="10" t="inlineStr">
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>成分名</t>
         </is>
       </c>
+      <c r="B9" s="2" t="n"/>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>原単位</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>秤量者</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>原料ロット</t>
         </is>
       </c>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="5" t="n"/>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>確認者</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="2" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="5" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="2" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="5" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="2" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="4" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="5" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="2" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="5" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="2" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="5" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="2" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="5" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="2" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="5" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="2" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="5" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="2" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="5" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="5" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="5" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="2" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="5" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="2" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="5" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="5" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="6" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B13:D13"/>
+  <mergeCells count="36">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
